--- a/data/trans_dic/IP29_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 33,54</t>
+          <t>21,36; 34,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,16; 38,96</t>
+          <t>25,92; 39,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 44,81</t>
+          <t>30,79; 44,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,36; 32,7</t>
+          <t>19,98; 31,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 35,38</t>
+          <t>23,19; 36,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,74; 44,93</t>
+          <t>30,77; 43,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,89; 30,61</t>
+          <t>21,77; 30,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,83; 34,82</t>
+          <t>25,79; 34,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,94; 42,04</t>
+          <t>32,27; 42,08</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,91; 40,36</t>
+          <t>29,32; 39,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,11; 31,39</t>
+          <t>22,03; 31,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 35,69</t>
+          <t>25,38; 35,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,14; 33,04</t>
+          <t>23,52; 33,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 27,61</t>
+          <t>18,03; 27,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,88; 36,91</t>
+          <t>27,06; 37,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,73; 35,14</t>
+          <t>27,88; 34,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 28,28</t>
+          <t>21,22; 28,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 34,92</t>
+          <t>27,44; 34,72</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,77; 36,64</t>
+          <t>24,4; 36,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,17; 31,9</t>
+          <t>20,78; 32,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,84; 34,09</t>
+          <t>22,9; 34,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 32,3</t>
+          <t>20,24; 32,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,55; 28,8</t>
+          <t>18,21; 29,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,6; 33,55</t>
+          <t>22,65; 33,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,9; 32,21</t>
+          <t>23,97; 32,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,91; 28,69</t>
+          <t>20,95; 28,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,2</t>
+          <t>24,15; 32,03</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,2; 38,52</t>
+          <t>26,73; 38,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 29,89</t>
+          <t>19,76; 30,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 28,41</t>
+          <t>18,06; 28,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,5; 38,54</t>
+          <t>27,98; 38,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 27,51</t>
+          <t>17,59; 27,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,83; 30,92</t>
+          <t>21,07; 31,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 36,48</t>
+          <t>28,95; 36,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 27,46</t>
+          <t>20,11; 26,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 28,03</t>
+          <t>20,69; 28,14</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,5; 34,17</t>
+          <t>28,75; 34,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,09; 29,57</t>
+          <t>24,47; 29,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 32,11</t>
+          <t>26,39; 31,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,83; 31,49</t>
+          <t>25,89; 31,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,33; 26,42</t>
+          <t>21,24; 26,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,57; 33,49</t>
+          <t>27,66; 33,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,97; 32,08</t>
+          <t>28,14; 32,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,35; 27,35</t>
+          <t>23,44; 27,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,83; 31,77</t>
+          <t>27,68; 31,76</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>35963</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43259</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37365</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42754</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53628</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73328</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>86013</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>102617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>28329; 45166</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35186; 53638</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40233; 58532</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29114; 46039</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>34396; 54304</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>44599; 63755</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>60592; 84384</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>73252; 99132</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>88953; 115989</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>64911</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53043</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61752</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59672</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49103</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69846</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>124583</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>102146</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>131598</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>55341; 75001</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44048; 62575</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>51402; 72123</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49085; 69737</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39336; 58902</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>59469; 82118</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>110804; 137736</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>88733; 117501</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>115882; 146586</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>40681</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39674</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42929</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37532</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37281</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45927</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78213</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>76955</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>88855</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>33006; 49854</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31313; 48674</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34919; 52449</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29111; 46073</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>29491; 47223</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>36870; 55252</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>66903; 90989</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>65487; 89733</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>76140; 100967</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>63545</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51934</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46112</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45346</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51353</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>127810</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>97280</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>97465</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>52423; 74992</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41261; 63341</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>36241; 57178</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55169; 75266</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>36054; 57356</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>42066; 62321</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>113859; 144744</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>83226; 111619</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>82828; 112682</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>205100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>187911</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>199781</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>403934</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>362394</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>187669; 226564</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>170146; 207315</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>181116; 217984</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>180081; 218392</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>155737; 194490</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>201162; 240839</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>379329; 433388</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>334877; 392290</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>391273; 448977</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP29_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,36; 34,06</t>
+          <t>20,81; 33,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,92; 39,52</t>
+          <t>25,95; 39,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,79; 44,79</t>
+          <t>30,25; 44,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 31,6</t>
+          <t>19,89; 31,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,19; 36,61</t>
+          <t>22,25; 35,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,77; 43,98</t>
+          <t>30,06; 43,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,77; 30,32</t>
+          <t>22,04; 31,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,79; 34,9</t>
+          <t>25,93; 35,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,27; 42,08</t>
+          <t>32,1; 42,37</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 39,73</t>
+          <t>29,19; 39,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 31,29</t>
+          <t>21,73; 31,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,62</t>
+          <t>26,03; 35,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 33,41</t>
+          <t>23,79; 33,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 27,0</t>
+          <t>18,18; 27,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,06; 37,37</t>
+          <t>26,69; 37,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,88; 34,65</t>
+          <t>27,84; 34,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,22; 28,1</t>
+          <t>20,99; 28,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,44; 34,72</t>
+          <t>27,95; 35,2</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,4; 36,85</t>
+          <t>24,28; 36,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,78; 32,3</t>
+          <t>20,81; 32,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,9; 34,4</t>
+          <t>22,89; 34,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 32,03</t>
+          <t>20,46; 32,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 29,16</t>
+          <t>17,88; 28,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 33,94</t>
+          <t>22,4; 33,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,97; 32,6</t>
+          <t>24,03; 32,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,95; 28,7</t>
+          <t>20,55; 28,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,15; 32,03</t>
+          <t>24,48; 32,74</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,73; 38,24</t>
+          <t>26,99; 38,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 30,33</t>
+          <t>20,08; 30,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,06; 28,49</t>
+          <t>18,23; 28,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,98; 38,17</t>
+          <t>27,26; 38,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 27,98</t>
+          <t>17,54; 27,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,07; 31,22</t>
+          <t>20,55; 31,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 36,8</t>
+          <t>28,95; 36,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 26,97</t>
+          <t>20,15; 27,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 28,14</t>
+          <t>21,1; 28,46</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,75; 34,71</t>
+          <t>28,54; 34,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,82</t>
+          <t>24,12; 29,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,76</t>
+          <t>26,51; 31,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 31,4</t>
+          <t>25,99; 31,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,24; 26,52</t>
+          <t>21,2; 26,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,66; 33,12</t>
+          <t>27,26; 33,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,14; 32,15</t>
+          <t>28,15; 32,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,44; 27,46</t>
+          <t>23,61; 27,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,68; 31,76</t>
+          <t>27,66; 31,72</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28329; 45166</t>
+          <t>27601; 44044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35186; 53638</t>
+          <t>35227; 53478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40233; 58532</t>
+          <t>39527; 58589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29114; 46039</t>
+          <t>28972; 45743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34396; 54304</t>
+          <t>33007; 53277</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44599; 63755</t>
+          <t>43569; 62739</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60592; 84384</t>
+          <t>61345; 86324</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73252; 99132</t>
+          <t>73657; 99983</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88953; 115989</t>
+          <t>88463; 116786</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55341; 75001</t>
+          <t>55097; 75371</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44048; 62575</t>
+          <t>43448; 62662</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51402; 72123</t>
+          <t>52714; 71929</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49085; 69737</t>
+          <t>49652; 70209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39336; 58902</t>
+          <t>39664; 59251</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59469; 82118</t>
+          <t>58659; 81411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>110804; 137736</t>
+          <t>110659; 139102</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88733; 117501</t>
+          <t>87756; 117543</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>115882; 146586</t>
+          <t>117999; 148645</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33006; 49854</t>
+          <t>32846; 49057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31313; 48674</t>
+          <t>31359; 48513</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34919; 52449</t>
+          <t>34904; 52255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29111; 46073</t>
+          <t>29432; 46902</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29491; 47223</t>
+          <t>28960; 46184</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36870; 55252</t>
+          <t>36462; 55290</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66903; 90989</t>
+          <t>67084; 89829</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65487; 89733</t>
+          <t>64251; 89814</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76140; 100967</t>
+          <t>77180; 103207</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52423; 74992</t>
+          <t>52936; 75987</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41261; 63341</t>
+          <t>41928; 63534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36241; 57178</t>
+          <t>36597; 57106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55169; 75266</t>
+          <t>53744; 76078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36054; 57356</t>
+          <t>35962; 55957</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42066; 62321</t>
+          <t>41024; 62081</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>113859; 144744</t>
+          <t>113867; 144837</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83226; 111619</t>
+          <t>83398; 113952</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82828; 112682</t>
+          <t>84478; 113954</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>187669; 226564</t>
+          <t>186301; 225741</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>170146; 207315</t>
+          <t>167710; 207091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181116; 217984</t>
+          <t>181939; 218783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180081; 218392</t>
+          <t>180744; 218650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155737; 194490</t>
+          <t>155443; 193585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>201162; 240839</t>
+          <t>198247; 240145</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>379329; 433388</t>
+          <t>379490; 432192</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>334877; 392290</t>
+          <t>337279; 388911</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>391273; 448977</t>
+          <t>390945; 448340</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP29_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>27,12%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>31,87%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,49%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 33,21</t>
+          <t>20,36; 32,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 39,4</t>
+          <t>22,45; 35,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,25; 44,84</t>
+          <t>30,74; 44,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,89; 31,4</t>
+          <t>21,15; 33,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,25; 35,92</t>
+          <t>25,16; 38,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,06; 43,28</t>
+          <t>30,31; 44,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,04; 31,02</t>
+          <t>21,89; 30,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,93; 35,2</t>
+          <t>25,83; 34,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,1; 42,37</t>
+          <t>31,94; 42,04</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>34,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>26,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>30,5%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 39,93</t>
+          <t>23,14; 33,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,73; 31,34</t>
+          <t>17,78; 27,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,03; 35,52</t>
+          <t>26,88; 36,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,79; 33,64</t>
+          <t>28,91; 40,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 27,16</t>
+          <t>22,11; 31,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 37,05</t>
+          <t>25,83; 35,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,84; 34,99</t>
+          <t>27,73; 35,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,99; 28,11</t>
+          <t>21,33; 28,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,95; 35,2</t>
+          <t>27,79; 34,92</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>30,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>26,33%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>28,16%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26,09%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,28; 36,26</t>
+          <t>20,7; 32,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 32,19</t>
+          <t>17,55; 28,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,89; 34,28</t>
+          <t>22,6; 33,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,46; 32,6</t>
+          <t>24,77; 36,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 28,52</t>
+          <t>20,17; 31,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,4; 33,96</t>
+          <t>22,84; 34,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,03; 32,18</t>
+          <t>23,9; 32,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,55; 28,73</t>
+          <t>20,91; 28,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,48; 32,74</t>
+          <t>23,75; 32,2</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,12%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>32,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22,97%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 38,75</t>
+          <t>27,5; 38,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,08; 30,43</t>
+          <t>17,18; 27,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 28,45</t>
+          <t>20,83; 30,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 38,58</t>
+          <t>27,2; 38,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,54; 27,3</t>
+          <t>19,9; 29,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 31,1</t>
+          <t>18,02; 28,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 36,83</t>
+          <t>28,67; 36,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,15; 27,54</t>
+          <t>20,1; 27,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,1; 28,46</t>
+          <t>20,59; 28,03</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,58</t>
+          <t>25,83; 31,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,12; 29,79</t>
+          <t>21,33; 26,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,51; 31,88</t>
+          <t>27,57; 33,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,99; 31,44</t>
+          <t>28,5; 34,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,2; 26,4</t>
+          <t>24,09; 29,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,26; 33,03</t>
+          <t>26,45; 32,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,15; 32,06</t>
+          <t>27,97; 32,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,61; 27,22</t>
+          <t>23,35; 27,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,66; 31,72</t>
+          <t>27,83; 31,77</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37365</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42754</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53628</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>35963</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>43259</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>48988</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37365</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>42754</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53628</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27601; 44044</t>
+          <t>29658; 47647</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35227; 53478</t>
+          <t>33304; 52471</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39527; 58589</t>
+          <t>44567; 65126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28972; 45743</t>
+          <t>28043; 44481</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33007; 53277</t>
+          <t>34151; 52881</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43569; 62739</t>
+          <t>39602; 58547</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61345; 86324</t>
+          <t>60920; 85187</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73657; 99983</t>
+          <t>73359; 98900</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88463; 116786</t>
+          <t>88034; 115882</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59672</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49103</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69846</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>64911</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>53043</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>61752</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59672</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49103</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69846</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55097; 75371</t>
+          <t>48298; 68951</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43448; 62662</t>
+          <t>38774; 60229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52714; 71929</t>
+          <t>59060; 81098</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49652; 70209</t>
+          <t>54570; 76185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39664; 59251</t>
+          <t>44202; 62771</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58659; 81411</t>
+          <t>52308; 72264</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>110659; 139102</t>
+          <t>110213; 139667</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87756; 117543</t>
+          <t>89166; 118235</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117999; 148645</t>
+          <t>117348; 147446</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>37532</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37281</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45927</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>40681</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>39674</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>42929</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37532</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>37281</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45927</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32846; 49057</t>
+          <t>29778; 46458</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31359; 48513</t>
+          <t>28415; 46632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34904; 52255</t>
+          <t>36793; 54616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29432; 46902</t>
+          <t>33505; 49564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28960; 46184</t>
+          <t>30402; 48073</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36462; 55290</t>
+          <t>34824; 51969</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67084; 89829</t>
+          <t>66710; 89913</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64251; 89814</t>
+          <t>65369; 89706</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77180; 103207</t>
+          <t>74882; 101502</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45346</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51353</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>63545</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>51934</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>46112</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>64265</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>45346</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51353</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52936; 75987</t>
+          <t>54220; 75985</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41928; 63534</t>
+          <t>35230; 56392</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36597; 57106</t>
+          <t>41587; 61735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53744; 76078</t>
+          <t>53348; 75539</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35962; 55957</t>
+          <t>41561; 62416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41024; 62081</t>
+          <t>36164; 57022</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>113867; 144837</t>
+          <t>112751; 143471</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83398; 113952</t>
+          <t>83189; 113627</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84478; 113954</t>
+          <t>82431; 112220</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>269</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>301</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>199781</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>198834</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>174484</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>186301; 225741</t>
+          <t>179601; 218963</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>167710; 207091</t>
+          <t>156425; 193734</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181939; 218783</t>
+          <t>200495; 243531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180744; 218650</t>
+          <t>186056; 223047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155443; 193585</t>
+          <t>167451; 205543</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>198247; 240145</t>
+          <t>181532; 220370</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>379490; 432192</t>
+          <t>377129; 432518</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>337279; 388911</t>
+          <t>333567; 390742</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>390945; 448340</t>
+          <t>393370; 449071</t>
         </is>
       </c>
     </row>
